--- a/Assets/ShooterSurvival/GameData/Editor/Data.xlsx
+++ b/Assets/ShooterSurvival/GameData/Editor/Data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ljh\tralalero Shooter\Assets\ShooterSurvival\GameData\Editor\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2976FD6-9A4B-45CF-B125-A89E8E379DA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F44673AB-00BE-4F12-B776-1270DCC641A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="업그레이드" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2765" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2797" uniqueCount="161">
   <si>
     <t>식별 순번</t>
   </si>
@@ -466,6 +466,102 @@
   </si>
   <si>
     <t>최종 체력</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이름</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공격력</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사거리</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>체력</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>퉁퉁퉁</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>붐바르</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>미사일</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>별칭</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>날카로운 일격</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전투 본능</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>속사 태세</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>장거리 탄</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>든든항 생명</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>생존 본능</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>지상 지원군</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공중 지원군</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다중 탄막</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>파멸의 일격</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>광전사의 힘</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>폭풍 속사</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>초월 사격</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>불굴의 생명</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>철벽의 생존</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공속</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -8194,15 +8290,16 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="B2:L132"/>
+  <dimension ref="B2:N132"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="18.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13" customWidth="1"/>
-    <col min="10" max="10" width="25.75" customWidth="1"/>
+    <col min="5" max="5" width="14.25" customWidth="1"/>
+    <col min="7" max="7" width="13" customWidth="1"/>
+    <col min="12" max="12" width="25.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -8213,31 +8310,37 @@
         <v>2</v>
       </c>
       <c r="E2" t="s">
+        <v>144</v>
+      </c>
+      <c r="F2" t="s">
+        <v>137</v>
+      </c>
+      <c r="G2" t="s">
         <v>3</v>
       </c>
-      <c r="F2" t="s">
+      <c r="H2" t="s">
         <v>4</v>
       </c>
-      <c r="G2" t="s">
+      <c r="I2" t="s">
         <v>5</v>
       </c>
-      <c r="H2" t="s">
+      <c r="J2" t="s">
         <v>6</v>
       </c>
-      <c r="I2" t="s">
+      <c r="K2" t="s">
         <v>7</v>
       </c>
-      <c r="J2" t="s">
+      <c r="L2" t="s">
         <v>8</v>
       </c>
-      <c r="K2" t="s">
+      <c r="M2" t="s">
         <v>56</v>
       </c>
-      <c r="L2" t="s">
+      <c r="N2" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B3">
         <v>1</v>
       </c>
@@ -8248,19 +8351,25 @@
         <v>1</v>
       </c>
       <c r="E3" t="s">
+        <v>145</v>
+      </c>
+      <c r="F3" t="s">
+        <v>138</v>
+      </c>
+      <c r="G3" t="s">
         <v>59</v>
       </c>
-      <c r="G3" t="s">
+      <c r="I3" t="s">
         <v>60</v>
       </c>
-      <c r="K3" s="3">
+      <c r="M3" s="3">
         <v>0.12</v>
       </c>
-      <c r="L3" s="3">
+      <c r="N3" s="3">
         <v>0.18</v>
       </c>
     </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B4">
         <v>2</v>
       </c>
@@ -8271,19 +8380,25 @@
         <v>1</v>
       </c>
       <c r="E4" t="s">
+        <v>146</v>
+      </c>
+      <c r="F4" t="s">
+        <v>138</v>
+      </c>
+      <c r="G4" t="s">
         <v>61</v>
       </c>
-      <c r="G4" t="s">
+      <c r="I4" t="s">
         <v>19</v>
       </c>
-      <c r="K4" s="4">
+      <c r="M4" s="4">
         <v>10</v>
       </c>
-      <c r="L4" s="4">
+      <c r="N4" s="4">
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B5">
         <v>3</v>
       </c>
@@ -8294,19 +8409,25 @@
         <v>1</v>
       </c>
       <c r="E5" t="s">
+        <v>147</v>
+      </c>
+      <c r="F5" t="s">
+        <v>160</v>
+      </c>
+      <c r="G5" t="s">
         <v>62</v>
       </c>
-      <c r="G5" t="s">
+      <c r="I5" t="s">
         <v>19</v>
       </c>
-      <c r="K5" s="6">
+      <c r="M5" s="6">
         <v>8</v>
       </c>
-      <c r="L5" s="6">
+      <c r="N5" s="6">
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B6">
         <v>4</v>
       </c>
@@ -8317,19 +8438,25 @@
         <v>1</v>
       </c>
       <c r="E6" t="s">
+        <v>148</v>
+      </c>
+      <c r="F6" t="s">
+        <v>139</v>
+      </c>
+      <c r="G6" t="s">
         <v>63</v>
       </c>
-      <c r="G6" t="s">
+      <c r="I6" t="s">
         <v>19</v>
       </c>
-      <c r="K6" s="7">
+      <c r="M6" s="7">
         <v>15</v>
       </c>
-      <c r="L6" s="7">
+      <c r="N6" s="7">
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B7">
         <v>5</v>
       </c>
@@ -8340,19 +8467,25 @@
         <v>1</v>
       </c>
       <c r="E7" t="s">
+        <v>149</v>
+      </c>
+      <c r="F7" t="s">
+        <v>140</v>
+      </c>
+      <c r="G7" t="s">
         <v>64</v>
       </c>
-      <c r="G7" t="s">
+      <c r="I7" t="s">
         <v>60</v>
       </c>
-      <c r="K7" s="8">
+      <c r="M7" s="8">
         <v>0.12</v>
       </c>
-      <c r="L7" s="8">
+      <c r="N7" s="8">
         <v>0.2</v>
       </c>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B8">
         <v>6</v>
       </c>
@@ -8363,19 +8496,25 @@
         <v>1</v>
       </c>
       <c r="E8" t="s">
+        <v>150</v>
+      </c>
+      <c r="F8" t="s">
+        <v>140</v>
+      </c>
+      <c r="G8" t="s">
         <v>65</v>
       </c>
-      <c r="G8" t="s">
+      <c r="I8" t="s">
         <v>19</v>
       </c>
-      <c r="K8" s="9">
+      <c r="M8" s="9">
         <v>10</v>
       </c>
-      <c r="L8" s="9">
+      <c r="N8" s="9">
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B9">
         <v>7</v>
       </c>
@@ -8386,19 +8525,25 @@
         <v>1</v>
       </c>
       <c r="E9" t="s">
+        <v>151</v>
+      </c>
+      <c r="F9" t="s">
+        <v>141</v>
+      </c>
+      <c r="G9" t="s">
         <v>67</v>
       </c>
-      <c r="G9" t="s">
+      <c r="I9" t="s">
         <v>11</v>
       </c>
-      <c r="K9">
+      <c r="M9">
         <v>1</v>
       </c>
-      <c r="L9">
+      <c r="N9">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B10">
         <v>8</v>
       </c>
@@ -8409,19 +8554,25 @@
         <v>1</v>
       </c>
       <c r="E10" t="s">
+        <v>152</v>
+      </c>
+      <c r="F10" t="s">
+        <v>142</v>
+      </c>
+      <c r="G10" t="s">
         <v>68</v>
       </c>
-      <c r="G10" t="s">
+      <c r="I10" t="s">
         <v>11</v>
       </c>
-      <c r="K10">
+      <c r="M10">
         <v>1</v>
       </c>
-      <c r="L10">
+      <c r="N10">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B11">
         <v>9</v>
       </c>
@@ -8432,19 +8583,25 @@
         <v>1</v>
       </c>
       <c r="E11" t="s">
+        <v>153</v>
+      </c>
+      <c r="F11" t="s">
+        <v>143</v>
+      </c>
+      <c r="G11" t="s">
         <v>70</v>
       </c>
-      <c r="G11" t="s">
+      <c r="I11" t="s">
         <v>11</v>
       </c>
-      <c r="K11">
+      <c r="M11">
         <v>1</v>
       </c>
-      <c r="L11">
+      <c r="N11">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B12">
         <v>10</v>
       </c>
@@ -8455,21 +8612,27 @@
         <v>1</v>
       </c>
       <c r="E12" t="s">
+        <v>154</v>
+      </c>
+      <c r="F12" t="s">
+        <v>138</v>
+      </c>
+      <c r="G12" t="s">
         <v>59</v>
       </c>
-      <c r="G12" t="s">
+      <c r="I12" t="s">
         <v>60</v>
       </c>
-      <c r="K12" s="3">
-        <f>K3*3</f>
+      <c r="M12" s="3">
+        <f>M3*3</f>
         <v>0.36</v>
       </c>
-      <c r="L12" s="3">
-        <f>K12*1.5</f>
+      <c r="N12" s="3">
+        <f>M12*1.5</f>
         <v>0.54</v>
       </c>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B13">
         <v>11</v>
       </c>
@@ -8480,21 +8643,27 @@
         <v>1</v>
       </c>
       <c r="E13" t="s">
+        <v>155</v>
+      </c>
+      <c r="F13" t="s">
+        <v>138</v>
+      </c>
+      <c r="G13" t="s">
         <v>61</v>
       </c>
-      <c r="G13" t="s">
+      <c r="I13" t="s">
         <v>19</v>
       </c>
-      <c r="K13" s="4">
-        <f t="shared" ref="K13:K17" si="0">K4*3</f>
+      <c r="M13" s="4">
+        <f t="shared" ref="M13:M17" si="0">M4*3</f>
         <v>30</v>
       </c>
-      <c r="L13" s="4">
-        <f t="shared" ref="L13:L17" si="1">K13*1.5</f>
+      <c r="N13" s="4">
+        <f t="shared" ref="N13:N17" si="1">M13*1.5</f>
         <v>45</v>
       </c>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B14">
         <v>12</v>
       </c>
@@ -8505,21 +8674,27 @@
         <v>1</v>
       </c>
       <c r="E14" t="s">
+        <v>156</v>
+      </c>
+      <c r="F14" t="s">
+        <v>160</v>
+      </c>
+      <c r="G14" t="s">
         <v>62</v>
       </c>
-      <c r="G14" t="s">
+      <c r="I14" t="s">
         <v>19</v>
       </c>
-      <c r="K14" s="6">
+      <c r="M14" s="6">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="L14" s="6">
+      <c r="N14" s="6">
         <f t="shared" si="1"/>
         <v>36</v>
       </c>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B15">
         <v>13</v>
       </c>
@@ -8530,21 +8705,27 @@
         <v>1</v>
       </c>
       <c r="E15" t="s">
+        <v>157</v>
+      </c>
+      <c r="F15" t="s">
+        <v>139</v>
+      </c>
+      <c r="G15" t="s">
         <v>63</v>
       </c>
-      <c r="G15" t="s">
+      <c r="I15" t="s">
         <v>19</v>
       </c>
-      <c r="K15" s="7">
+      <c r="M15" s="7">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
-      <c r="L15" s="7">
-        <f>ROUND(K15*1.5,0)</f>
+      <c r="N15" s="7">
+        <f>ROUND(M15*1.5,0)</f>
         <v>68</v>
       </c>
     </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B16">
         <v>14</v>
       </c>
@@ -8555,21 +8736,27 @@
         <v>1</v>
       </c>
       <c r="E16" t="s">
+        <v>158</v>
+      </c>
+      <c r="F16" t="s">
+        <v>140</v>
+      </c>
+      <c r="G16" t="s">
         <v>64</v>
       </c>
-      <c r="G16" t="s">
+      <c r="I16" t="s">
         <v>60</v>
       </c>
-      <c r="K16" s="8">
+      <c r="M16" s="8">
         <f t="shared" si="0"/>
         <v>0.36</v>
       </c>
-      <c r="L16" s="8">
+      <c r="N16" s="8">
         <f t="shared" si="1"/>
         <v>0.54</v>
       </c>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B17">
         <v>15</v>
       </c>
@@ -8580,50 +8767,56 @@
         <v>1</v>
       </c>
       <c r="E17" t="s">
+        <v>159</v>
+      </c>
+      <c r="F17" t="s">
+        <v>140</v>
+      </c>
+      <c r="G17" t="s">
         <v>65</v>
       </c>
-      <c r="G17" t="s">
+      <c r="I17" t="s">
         <v>19</v>
       </c>
-      <c r="K17" s="9">
+      <c r="M17" s="9">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="L17" s="9">
+      <c r="N17" s="9">
         <f t="shared" si="1"/>
         <v>45</v>
       </c>
     </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="E23" s="5"/>
-      <c r="H23" s="5"/>
-    </row>
-    <row r="124" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E124" s="1"/>
-    </row>
-    <row r="125" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E125" s="1"/>
-    </row>
-    <row r="126" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E126" s="1"/>
-    </row>
-    <row r="127" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E127" s="1"/>
-    </row>
-    <row r="128" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E128" s="1"/>
-    </row>
-    <row r="129" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E129" s="1"/>
-    </row>
-    <row r="130" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E130" s="1"/>
-    </row>
-    <row r="131" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E131" s="1"/>
-    </row>
-    <row r="132" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E132" s="1"/>
+    <row r="23" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="G23" s="5"/>
+      <c r="J23" s="5"/>
+    </row>
+    <row r="124" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G124" s="1"/>
+    </row>
+    <row r="125" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G125" s="1"/>
+    </row>
+    <row r="126" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G126" s="1"/>
+    </row>
+    <row r="127" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G127" s="1"/>
+    </row>
+    <row r="128" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G128" s="1"/>
+    </row>
+    <row r="129" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G129" s="1"/>
+    </row>
+    <row r="130" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G130" s="1"/>
+    </row>
+    <row r="131" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G131" s="1"/>
+    </row>
+    <row r="132" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G132" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
